--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A58D0FD1-E4EF-464F-9C70-F17A86BE8926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7C44A23-6762-4EC0-845E-5EB0024DB231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1770" yWindow="3420" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
   <si>
     <t>id</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>Ocho doble|As de guía|Nudo de rizo o llano|Nudo ballestrinque</t>
-  </si>
-  <si>
-    <t>º</t>
   </si>
   <si>
     <t>La habilidad, disciplina o arte que conseguimos con el uso de las cuerdas haciendo nudos se llama?</t>
@@ -553,13 +550,13 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
       <c r="F3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -576,10 +573,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -589,22 +586,31 @@
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
-        <v>16</v>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
         <v>7</v>
       </c>
     </row>
@@ -612,40 +618,64 @@
       <c r="A9">
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
+      <c r="B13" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
+      <c r="B14" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
+      <c r="B15" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7C44A23-6762-4EC0-845E-5EB0024DB231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCEB2C91-2DF3-4031-9A8F-1AE00860E1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="3420" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-27330" yWindow="2460" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
   <si>
     <t>id</t>
   </si>
@@ -96,6 +96,12 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudorizoollano.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El nudo de ocho doble es un nudo seguro y rápido de revisar. Lo usamos para unirnos al arnés de escalada entre otras utilidades. Haz un ocho doble y sube la imagen. </t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochodoble.jpg</t>
   </si>
 </sst>
 </file>
@@ -483,7 +489,7 @@
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="101.140625" customWidth="1"/>
+    <col min="4" max="4" width="192.7109375" customWidth="1"/>
     <col min="5" max="5" width="72.140625" customWidth="1"/>
     <col min="6" max="6" width="79.7109375" customWidth="1"/>
     <col min="7" max="7" width="79.28515625" customWidth="1"/>
@@ -589,6 +595,18 @@
       <c r="B5" t="s">
         <v>7</v>
       </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
@@ -748,6 +766,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{66CBA43C-94AC-4AFE-9716-4FCF48371297}"/>
+    <hyperlink ref="G5" r:id="rId2" xr:uid="{2199C3B7-0EA7-45E3-865C-9EFEDF0DCCC0}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{66451763-92B9-4252-AD34-2AF38B17D299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C5B379-2675-423F-B32B-560E7F11F823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27330" yWindow="2460" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="1125" yWindow="1425" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
   <si>
     <t>id</t>
   </si>
@@ -102,6 +102,12 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochodoble.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El nudo tejedor o vuelta de escota es el que utilizamos par unir dos cuerdas de grosores distintos. Coge dos cuerdas y haz este nudo y sube la imagen. </t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudovueltadeescota.jpg</t>
   </si>
 </sst>
 </file>
@@ -615,6 +621,18 @@
       <c r="B6" t="s">
         <v>7</v>
       </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6">
+        <v>5</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
@@ -623,6 +641,9 @@
       <c r="B7" t="s">
         <v>7</v>
       </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -630,6 +651,9 @@
       </c>
       <c r="B8" t="s">
         <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -638,6 +662,9 @@
       </c>
       <c r="B9" t="s">
         <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -767,6 +794,7 @@
   <hyperlinks>
     <hyperlink ref="G4" r:id="rId1" xr:uid="{66CBA43C-94AC-4AFE-9716-4FCF48371297}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{2199C3B7-0EA7-45E3-865C-9EFEDF0DCCC0}"/>
+    <hyperlink ref="G6" r:id="rId3" xr:uid="{89FEB521-AD4C-4B1D-94FB-105036FDE573}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C5B379-2675-423F-B32B-560E7F11F823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B64ED6-6F13-4150-B03C-4EC2E2E08F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1425" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="25">
   <si>
     <t>id</t>
   </si>
@@ -92,15 +92,9 @@
     <t>Búlder|Trepa|Cabuyería|Trenzar</t>
   </si>
   <si>
-    <t>El nudo de rizo o nudo llano sirve para unir dos cuerdas del mismo grosor. Haz un nudo de rizo y sube la imagen.</t>
-  </si>
-  <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudorizoollano.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">El nudo de ocho doble es un nudo seguro y rápido de revisar. Lo usamos para unirnos al arnés de escalada entre otras utilidades. Haz un ocho doble y sube la imagen. </t>
-  </si>
-  <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochodoble.jpg</t>
   </si>
   <si>
@@ -108,6 +102,15 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudovueltadeescota.jpg</t>
+  </si>
+  <si>
+    <t>El Nudo de Rizo o Nudo Llano sirve para unir dos cuerdas del mismo grosor. Haz un nudo de rizo y sube la imagen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Nudo de Ocho Doble es un nudo seguro y rápido de revisar. Lo usamos para unirnos al arnés de escalada entre otras utilidades. Haz un ocho doble y sube la imagen. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Nudo Tejedor o Vuelta de Escota es el que utilizamos par unir dos cuerdas de grosores distintos. Coge dos cuerdas y haz este nudo y sube la imagen. </t>
   </si>
 </sst>
 </file>
@@ -585,10 +588,10 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="H4">
         <v>5</v>
@@ -605,10 +608,10 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -625,10 +628,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>5</v>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B64ED6-6F13-4150-B03C-4EC2E2E08F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9308E429-B42D-4D2A-B5AA-E539C8F61C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1425" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
   <si>
     <t>id</t>
   </si>
@@ -98,9 +98,6 @@
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochodoble.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">El nudo tejedor o vuelta de escota es el que utilizamos par unir dos cuerdas de grosores distintos. Coge dos cuerdas y haz este nudo y sube la imagen. </t>
-  </si>
-  <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudovueltadeescota.jpg</t>
   </si>
   <si>
@@ -111,13 +108,25 @@
   </si>
   <si>
     <t xml:space="preserve">El Nudo Tejedor o Vuelta de Escota es el que utilizamos par unir dos cuerdas de grosores distintos. Coge dos cuerdas y haz este nudo y sube la imagen. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Nudo de Ocho Simple es un nudo de tope fundamental y seguro, utilizado principalmente para evitar que un cabo se deslice a través de poleas. Es fácil de hacer, reconocer y deshacer. Necesario  para aprender a realizar el Nudo de Ocho Doble. Haz un Nudo de Ocho Simple y sube la imagen. </t>
+  </si>
+  <si>
+    <t>El nudo de ballestrinque es un nudo que se utiliza para afirmar un cabo con rapidez a un pasamanos, poste o argolla. Es un nudo fácil de ajustar y deshacer. Haz un ballestrinque en una pica, espaldera, poste… y sube la imagen.</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochosimple.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudoballestrinque.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,6 +138,13 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -155,9 +171,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -498,10 +515,10 @@
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="192.7109375" customWidth="1"/>
-    <col min="5" max="5" width="72.140625" customWidth="1"/>
+    <col min="4" max="4" width="182.42578125" customWidth="1"/>
+    <col min="5" max="5" width="114.28515625" customWidth="1"/>
     <col min="6" max="6" width="79.7109375" customWidth="1"/>
-    <col min="7" max="7" width="79.28515625" customWidth="1"/>
+    <col min="7" max="7" width="94.140625" customWidth="1"/>
     <col min="8" max="8" width="42.28515625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -588,7 +605,7 @@
         <v>11</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>18</v>
@@ -608,7 +625,7 @@
         <v>11</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>19</v>
@@ -628,10 +645,10 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -647,6 +664,15 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
+      <c r="D7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7">
+        <v>5</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
@@ -657,6 +683,15 @@
       </c>
       <c r="C8" t="s">
         <v>11</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -798,6 +833,8 @@
     <hyperlink ref="G4" r:id="rId1" xr:uid="{66CBA43C-94AC-4AFE-9716-4FCF48371297}"/>
     <hyperlink ref="G5" r:id="rId2" xr:uid="{2199C3B7-0EA7-45E3-865C-9EFEDF0DCCC0}"/>
     <hyperlink ref="G6" r:id="rId3" xr:uid="{89FEB521-AD4C-4B1D-94FB-105036FDE573}"/>
+    <hyperlink ref="G7" r:id="rId4" xr:uid="{902E4DDA-E2C0-44CF-AA3E-BBB28D70EC0D}"/>
+    <hyperlink ref="G8" r:id="rId5" xr:uid="{66411122-3CDC-43ED-96AF-B99C2ABE25FB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9308E429-B42D-4D2A-B5AA-E539C8F61C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BFF5345-D066-4495-9C78-A3D31C722A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1125" yWindow="1425" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>id</t>
   </si>
@@ -120,6 +120,12 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudoballestrinque.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Doble Pescador es un nudo habitual para unir dos cuerdas, o cerrar una misma en un anillo, lo cual posibilita el uso de este en múltiples utilidades. Haz un Doble Pescador y sube la imagen. </t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodoblepescador.jpg</t>
   </si>
 </sst>
 </file>
@@ -704,6 +710,15 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
+      <c r="D9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -835,6 +850,7 @@
     <hyperlink ref="G6" r:id="rId3" xr:uid="{89FEB521-AD4C-4B1D-94FB-105036FDE573}"/>
     <hyperlink ref="G7" r:id="rId4" xr:uid="{902E4DDA-E2C0-44CF-AA3E-BBB28D70EC0D}"/>
     <hyperlink ref="G8" r:id="rId5" xr:uid="{66411122-3CDC-43ED-96AF-B99C2ABE25FB}"/>
+    <hyperlink ref="G9" r:id="rId6" xr:uid="{B63DF6AB-7391-4ABC-B7A6-5753F290BE6A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BFF5345-D066-4495-9C78-A3D31C722A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{311BCB8B-137B-4676-A520-666B9A7B8446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1425" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-28035" yWindow="1380" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>id</t>
   </si>
@@ -126,6 +126,34 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodoblepescador.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudovueltadebraza.jpg</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>El Nudo Vuelta de Braza o Nudo Leñador sirve principalmente para asegurar una cuerda de forma rápida y segura a troncos, postes, maderas o ramas para arrastrarlos, elevarlos o fijarlos.  Haz el nudo y sube la imagen</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partesdeuncabo.jpg</t>
   </si>
 </sst>
 </file>
@@ -596,6 +624,9 @@
       <c r="F3">
         <v>2</v>
       </c>
+      <c r="G3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="H3">
         <v>5</v>
       </c>
@@ -726,6 +757,18 @@
       </c>
       <c r="B10" t="s">
         <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -851,6 +894,8 @@
     <hyperlink ref="G7" r:id="rId4" xr:uid="{902E4DDA-E2C0-44CF-AA3E-BBB28D70EC0D}"/>
     <hyperlink ref="G8" r:id="rId5" xr:uid="{66411122-3CDC-43ED-96AF-B99C2ABE25FB}"/>
     <hyperlink ref="G9" r:id="rId6" xr:uid="{B63DF6AB-7391-4ABC-B7A6-5753F290BE6A}"/>
+    <hyperlink ref="G10" r:id="rId7" xr:uid="{B28EBE25-725C-49E7-BA59-D8A777EAA066}"/>
+    <hyperlink ref="G3" r:id="rId8" xr:uid="{84CF5294-D3F1-4A25-9498-9DFFB7473435}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{311BCB8B-137B-4676-A520-666B9A7B8446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA8C43B3-CEB7-4794-A4D4-EAB6E1E05A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28035" yWindow="1380" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="1065" yWindow="3960" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
   <si>
     <t>id</t>
   </si>
@@ -111,9 +111,6 @@
   </si>
   <si>
     <t xml:space="preserve">El Nudo de Ocho Simple es un nudo de tope fundamental y seguro, utilizado principalmente para evitar que un cabo se deslice a través de poleas. Es fácil de hacer, reconocer y deshacer. Necesario  para aprender a realizar el Nudo de Ocho Doble. Haz un Nudo de Ocho Simple y sube la imagen. </t>
-  </si>
-  <si>
-    <t>El nudo de ballestrinque es un nudo que se utiliza para afirmar un cabo con rapidez a un pasamanos, poste o argolla. Es un nudo fácil de ajustar y deshacer. Haz un ballestrinque en una pica, espaldera, poste… y sube la imagen.</t>
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudodeochosimple.jpg</t>
@@ -155,12 +152,92 @@
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partesdeuncabo.jpg</t>
   </si>
+  <si>
+    <t>El Nudo de Ballestrinque es un nudo que se utiliza para afirmar un cabo con rapidez a un pasamanos, poste o argolla. Es un nudo fácil de ajustar y deshacer. Haz un Ballestrinque en una pica, espaldera, poste… y sube la imagen.</t>
+  </si>
+  <si>
+    <t>Tienes que unir dos cuerdas de grososres muy distintos. ¿Qué nudo utilizarías de los aprendidos en clase?</t>
+  </si>
+  <si>
+    <t>Ocho Doble|Vuelta de Escota|Nudo de Rizo o Llano|Nudo Ballestrinque</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudosportada.jpg</t>
+  </si>
+  <si>
+    <r>
+      <t>Las cuerdas en escalada se clasifican por su elongación: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>dinámicas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>semiestáticas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> y </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>estáticas</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t>. ¿Qué tipo de cuerdas son las únicas para escalada de primero o deportiva?</t>
+    </r>
+  </si>
+  <si>
+    <t>Estáticas|Dinámicas|Semiestáticas|Cualquier tipo de cuerda</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/tiposdecuerdas.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +259,19 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -205,10 +295,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -549,9 +647,9 @@
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="182.42578125" customWidth="1"/>
-    <col min="5" max="5" width="114.28515625" customWidth="1"/>
-    <col min="6" max="6" width="79.7109375" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" customWidth="1"/>
+    <col min="5" max="5" width="68.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="94.140625" customWidth="1"/>
     <col min="8" max="8" width="42.28515625" customWidth="1"/>
   </cols>
@@ -566,7 +664,7 @@
       <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -592,7 +690,7 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
@@ -615,7 +713,7 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
@@ -625,7 +723,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3">
         <v>5</v>
@@ -641,7 +739,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -651,7 +749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -661,7 +759,7 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -671,7 +769,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -681,7 +779,7 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -691,7 +789,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -701,17 +799,17 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H7">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -721,17 +819,17 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>25</v>
+      <c r="D8" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -741,17 +839,17 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="H9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -761,11 +859,11 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" t="s">
-        <v>31</v>
+      <c r="D10" s="3" t="s">
+        <v>30</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10">
         <v>5</v>
@@ -778,13 +876,46 @@
       <c r="B11" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E12" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12">
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -794,6 +925,7 @@
       <c r="B13" t="s">
         <v>7</v>
       </c>
+      <c r="D13" s="3"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -802,6 +934,7 @@
       <c r="B14" t="s">
         <v>7</v>
       </c>
+      <c r="D14" s="3"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -810,6 +943,7 @@
       <c r="B15" t="s">
         <v>7</v>
       </c>
+      <c r="D15" s="3"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -818,28 +952,33 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="3"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="3"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="3"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="3"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="3"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -849,39 +988,43 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="3"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="3"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="3"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D24" s="3"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
@@ -896,6 +1039,8 @@
     <hyperlink ref="G9" r:id="rId6" xr:uid="{B63DF6AB-7391-4ABC-B7A6-5753F290BE6A}"/>
     <hyperlink ref="G10" r:id="rId7" xr:uid="{B28EBE25-725C-49E7-BA59-D8A777EAA066}"/>
     <hyperlink ref="G3" r:id="rId8" xr:uid="{84CF5294-D3F1-4A25-9498-9DFFB7473435}"/>
+    <hyperlink ref="G11" r:id="rId9" xr:uid="{8DF2120E-DCC6-4788-BFC8-4D34C28DA26B}"/>
+    <hyperlink ref="G12" r:id="rId10" xr:uid="{5AF94854-3527-4562-928E-F41EA469CCB1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA8C43B3-CEB7-4794-A4D4-EAB6E1E05A74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{76043702-1659-492F-9315-94A2A6F76644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="3960" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-28920" yWindow="-1110" windowWidth="29040" windowHeight="15720" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -231,6 +231,18 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/tiposdecuerdas.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Después de haber escogido la vía, el escalador comprueba que la longitud de
+la cuerda es la adecuada. También comprueba que no hay una gran diferencia
+de peso con su asegurador. Antes de empezar, asegurador y escalador
+realizan una comprobación mutua del equipo. Esta acción se denomina en escalada: </t>
+  </si>
+  <si>
+    <t>Rapelar|Chapar|Partner Check|Asegurar</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partnercheck.jpg</t>
   </si>
 </sst>
 </file>
@@ -295,17 +307,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -642,12 +653,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{109BD254-8530-49D4-9A14-2EE9209AFC31}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="93.140625" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" style="3" customWidth="1"/>
     <col min="5" max="5" width="68.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="94.140625" customWidth="1"/>
@@ -749,7 +760,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -769,7 +780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -789,7 +800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -809,7 +820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -829,7 +840,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -849,7 +860,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -902,7 +913,7 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
         <v>36</v>
       </c>
       <c r="E12" t="s">
@@ -925,7 +936,7 @@
       <c r="B13" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="2"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -934,7 +945,7 @@
       <c r="B14" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -943,7 +954,7 @@
       <c r="B15" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="3"/>
+      <c r="D15" s="2"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -952,33 +963,33 @@
       <c r="B16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="3"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D16" s="2"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="D18" s="3"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D18" s="2"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="D20" s="3"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -988,46 +999,138 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="3"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="D24" s="3"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>24</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" t="s">
+        <v>10</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" t="s">
+        <v>40</v>
+      </c>
+      <c r="F25">
+        <v>2</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>25</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" t="s">
+        <v>10</v>
+      </c>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26</v>
       </c>
+      <c r="B27" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" t="s">
+        <v>10</v>
+      </c>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" t="s">
+        <v>10</v>
+      </c>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D37" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1041,6 +1144,7 @@
     <hyperlink ref="G3" r:id="rId8" xr:uid="{84CF5294-D3F1-4A25-9498-9DFFB7473435}"/>
     <hyperlink ref="G11" r:id="rId9" xr:uid="{8DF2120E-DCC6-4788-BFC8-4D34C28DA26B}"/>
     <hyperlink ref="G12" r:id="rId10" xr:uid="{5AF94854-3527-4562-928E-F41EA469CCB1}"/>
+    <hyperlink ref="G25" r:id="rId11" xr:uid="{BFD16636-4079-414F-AE76-F5F5AFBEF5D6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{76043702-1659-492F-9315-94A2A6F76644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C58ABD3-39C2-4398-B8FE-411632F4EFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-1110" windowWidth="29040" windowHeight="15720" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-28095" yWindow="1440" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
   <si>
     <t>id</t>
   </si>
@@ -243,6 +243,82 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partnercheck.jpg</t>
+  </si>
+  <si>
+    <t>En la imagen ves una acción que permite limitar las consecuencias de una caída del escalador en los
+primeros metros de escalada, antes de que haya mosquetoneado el primer
+punto de seguridad. No sirve para retener al escalador, pero permite
+evitar las consecuencias de una mala caída. Sabrías decir como se llama esa acción en escalada:</t>
+  </si>
+  <si>
+    <t>Rapelar|Asegurar|Partner Check|Portear</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/portear.jpg</t>
+  </si>
+  <si>
+    <t>En la imagen vemos la gestualidad universal par utilizar correctamente un aparato para asegurar (gri-gri, reverso…) esa posición de las manos es fundamental. ¿Qué accion nunca debemos hacer cuando estamos realizando esa maniobra de aseguramiento?</t>
+  </si>
+  <si>
+    <t>Soltar la mano de frenado|Fijarte en el compañero para dar cuerda o recoger|Mantener una posición estable en el suelo|Bajar el centro de gravedad y ampliar base de sustentación</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/manodefrenado.jpg</t>
+  </si>
+  <si>
+    <t>El rol del asegurador no se limita a dar cuerda rápidamente y en el momento oportuno. Al permanecer concentrado en el escalador, el asegurador puede ver los momentos de tensión que requieren la máxima precisión y capacidad de reacción. ¿Cuál va a ser la labor más importante durante la ascensión del compañero?</t>
+  </si>
+  <si>
+    <t>Vigilancia|Anticipación|Movilidad|Vigilancia, anticipación y movilidad</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/vigilanci.jpg</t>
+  </si>
+  <si>
+    <t>En caso de caída, independientemente del aparato utilizado, la acción
+que debemos hace para aumentar el rozamiento y frenar la caida es:</t>
+  </si>
+  <si>
+    <t>Saltar y levantar la mano de la cuerda|Agarrar la cuerda que va al escalador y la que sale del sistema de retención|No hay que hacer nada porque se bloquea con el descensor|Sujetar firmemente la cuerda lado frenado, y al mismo tiempo tirar de ella hacia abajo</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/caidaescalada.jpg</t>
+  </si>
+  <si>
+    <t>Agarradas a la cuerda que sujeta al arnés|Agarrando las presas por las que va pasando durante el descenso|Deben estar sin sujetar la cuerda y preparadas por si tienen colocarse en el muro en caso de deplome|Agarrando el nudo de ocho doble</t>
+  </si>
+  <si>
+    <t>Cuando el escalador está listo para descender, después de la señal acordada, se deja llevar por la cuerda y no tiene ninguna forma de controlar el descenso. Toda la responsabilidad de esta maniobra recae en el asegurador, que tiene la vida del escalador en sus manos .¿Cómo debe colocar las manos durante el descenso el escalador?</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/descenso.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/arnes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la siguiente imagen vemos un material que usamos en escalada que se denomina: </t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Grigri</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/mosquetonseguridad.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/grigri.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lineadevida.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/cintaesprexx.jpg</t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Pies de gato</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/piedegato.jpg</t>
   </si>
 </sst>
 </file>
@@ -929,65 +1005,213 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C13" t="s">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>7</v>
-      </c>
-      <c r="D14" s="2"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C14" t="s">
+        <v>10</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C15" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15">
+        <v>3</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+      <c r="C16" t="s">
+        <v>10</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16">
+        <v>3</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="B17" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17">
+        <v>2</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17">
+        <v>5</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" t="s">
+        <v>10</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E18" t="s">
+        <v>59</v>
+      </c>
+      <c r="F18">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="H18">
+        <v>5</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="B19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" t="s">
+        <v>10</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E19" t="s">
+        <v>59</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H19">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="B20" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H20">
+        <v>5</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21">
@@ -1061,7 +1285,21 @@
       <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="2"/>
+      <c r="D26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>59</v>
+      </c>
+      <c r="F26">
+        <v>3</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26">
+        <v>5</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27">
@@ -1073,7 +1311,21 @@
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="2"/>
+      <c r="D27" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E27" t="s">
+        <v>59</v>
+      </c>
+      <c r="F27">
+        <v>2</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H27">
+        <v>5</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28">
@@ -1085,7 +1337,21 @@
       <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28">
+        <v>4</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H28">
+        <v>5</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29">
@@ -1145,6 +1411,17 @@
     <hyperlink ref="G11" r:id="rId9" xr:uid="{8DF2120E-DCC6-4788-BFC8-4D34C28DA26B}"/>
     <hyperlink ref="G12" r:id="rId10" xr:uid="{5AF94854-3527-4562-928E-F41EA469CCB1}"/>
     <hyperlink ref="G25" r:id="rId11" xr:uid="{BFD16636-4079-414F-AE76-F5F5AFBEF5D6}"/>
+    <hyperlink ref="G13" r:id="rId12" xr:uid="{733418C9-9221-47D0-ACC2-F31A36FB4360}"/>
+    <hyperlink ref="G14" r:id="rId13" xr:uid="{60681CBF-66C1-40D5-926C-3E6DE320D630}"/>
+    <hyperlink ref="G15" r:id="rId14" xr:uid="{18CDDFA0-DBC0-482F-AA7E-EADE2231B19C}"/>
+    <hyperlink ref="G16" r:id="rId15" xr:uid="{19FF299A-4600-4BF7-998D-1A8845ED9CAD}"/>
+    <hyperlink ref="G17" r:id="rId16" xr:uid="{FB0E80D8-0B0E-4DB3-B5C8-A66510E9F3D1}"/>
+    <hyperlink ref="G18" r:id="rId17" xr:uid="{D98CA101-5960-4FE5-BA43-EFB5C59AF55D}"/>
+    <hyperlink ref="G19" r:id="rId18" xr:uid="{37B3199B-1CE9-4647-AC5F-6AE19CC06704}"/>
+    <hyperlink ref="G20" r:id="rId19" xr:uid="{BF5409AE-2AB9-494C-A48E-99A204F32A5C}"/>
+    <hyperlink ref="G26" r:id="rId20" xr:uid="{9F92CBA7-5E57-412F-BEA4-6893071DBB45}"/>
+    <hyperlink ref="G27" r:id="rId21" xr:uid="{8E1A4167-6259-4D9F-AE04-9B5E6C4ED88B}"/>
+    <hyperlink ref="G28" r:id="rId22" xr:uid="{2E8A41EB-EB16-48D9-AF87-44431ED6BA50}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C58ABD3-39C2-4398-B8FE-411632F4EFC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BEC6C3-7ECC-4E7A-B058-EC19097E6AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28095" yWindow="1440" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -275,50 +275,50 @@
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/vigilanci.jpg</t>
   </si>
   <si>
+    <t>Saltar y levantar la mano de la cuerda|Agarrar la cuerda que va al escalador y la que sale del sistema de retención|No hay que hacer nada porque se bloquea con el descensor|Sujetar firmemente la cuerda lado frenado, y al mismo tiempo tirar de ella hacia abajo</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/caidaescalada.jpg</t>
+  </si>
+  <si>
+    <t>Agarradas a la cuerda que sujeta al arnés|Agarrando las presas por las que va pasando durante el descenso|Deben estar sin sujetar la cuerda y preparadas por si tienen colocarse en el muro en caso de deplome|Agarrando el nudo de ocho doble</t>
+  </si>
+  <si>
+    <t>Cuando el escalador está listo para descender, después de la señal acordada, se deja llevar por la cuerda y no tiene ninguna forma de controlar el descenso. Toda la responsabilidad de esta maniobra recae en el asegurador, que tiene la vida del escalador en sus manos .¿Cómo debe colocar las manos durante el descenso el escalador?</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/descenso.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/arnes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la siguiente imagen vemos un material que usamos en escalada que se denomina: </t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Grigri</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/mosquetonseguridad.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/grigri.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lineadevida.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/cintaesprexx.jpg</t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Pies de gato</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/piedegato.jpg</t>
+  </si>
+  <si>
     <t>En caso de caída, independientemente del aparato utilizado, la acción
-que debemos hace para aumentar el rozamiento y frenar la caida es:</t>
-  </si>
-  <si>
-    <t>Saltar y levantar la mano de la cuerda|Agarrar la cuerda que va al escalador y la que sale del sistema de retención|No hay que hacer nada porque se bloquea con el descensor|Sujetar firmemente la cuerda lado frenado, y al mismo tiempo tirar de ella hacia abajo</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/caidaescalada.jpg</t>
-  </si>
-  <si>
-    <t>Agarradas a la cuerda que sujeta al arnés|Agarrando las presas por las que va pasando durante el descenso|Deben estar sin sujetar la cuerda y preparadas por si tienen colocarse en el muro en caso de deplome|Agarrando el nudo de ocho doble</t>
-  </si>
-  <si>
-    <t>Cuando el escalador está listo para descender, después de la señal acordada, se deja llevar por la cuerda y no tiene ninguna forma de controlar el descenso. Toda la responsabilidad de esta maniobra recae en el asegurador, que tiene la vida del escalador en sus manos .¿Cómo debe colocar las manos durante el descenso el escalador?</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/descenso.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/arnes.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la siguiente imagen vemos un material que usamos en escalada que se denomina: </t>
-  </si>
-  <si>
-    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Grigri</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/mosquetonseguridad.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/grigri.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lineadevida.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/cintaesprexx.jpg</t>
-  </si>
-  <si>
-    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Pies de gato</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/piedegato.jpg</t>
+que debemos hacer para aumentar el rozamiento y frenar la caida es:</t>
   </si>
 </sst>
 </file>
@@ -1094,16 +1094,16 @@
         <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -1120,16 +1120,16 @@
         <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -1146,16 +1146,16 @@
         <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" t="s">
         <v>58</v>
-      </c>
-      <c r="E18" t="s">
-        <v>59</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1172,16 +1172,16 @@
         <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" t="s">
         <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>59</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1198,16 +1198,16 @@
         <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" t="s">
         <v>58</v>
-      </c>
-      <c r="E20" t="s">
-        <v>59</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -1286,16 +1286,16 @@
         <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E26" t="s">
         <v>58</v>
-      </c>
-      <c r="E26" t="s">
-        <v>59</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -1312,16 +1312,16 @@
         <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" t="s">
         <v>58</v>
-      </c>
-      <c r="E27" t="s">
-        <v>59</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -1338,16 +1338,16 @@
         <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H28">
         <v>5</v>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{65BEC6C3-7ECC-4E7A-B058-EC19097E6AC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C86034B-7A91-4DD3-9BA1-76C3422984A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28095" yWindow="1440" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
@@ -128,35 +128,10 @@
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudovueltadebraza.jpg</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>El Nudo Vuelta de Braza o Nudo Leñador sirve principalmente para asegurar una cuerda de forma rápida y segura a troncos, postes, maderas o ramas para arrastrarlos, elevarlos o fijarlos.  Haz el nudo y sube la imagen</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partesdeuncabo.jpg</t>
   </si>
   <si>
     <t>El Nudo de Ballestrinque es un nudo que se utiliza para afirmar un cabo con rapidez a un pasamanos, poste o argolla. Es un nudo fácil de ajustar y deshacer. Haz un Ballestrinque en una pica, espaldera, poste… y sube la imagen.</t>
-  </si>
-  <si>
-    <t>Tienes que unir dos cuerdas de grososres muy distintos. ¿Qué nudo utilizarías de los aprendidos en clase?</t>
   </si>
   <si>
     <t>Ocho Doble|Vuelta de Escota|Nudo de Rizo o Llano|Nudo Ballestrinque</t>
@@ -320,6 +295,12 @@
     <t>En caso de caída, independientemente del aparato utilizado, la acción
 que debemos hacer para aumentar el rozamiento y frenar la caida es:</t>
   </si>
+  <si>
+    <t xml:space="preserve">El Nudo Vuelta de Braza o Nudo Leñador sirve principalmente para asegurar una cuerda de forma rápida y segura a troncos, postes, maderas o ramas para arrastrarlos, elevarlos o fijarlos.  Haz el nudo y sube la imagen. </t>
+  </si>
+  <si>
+    <t>Tienes que unir dos cuerdas de grosores muy distintos. ¿Qué nudo utilizarías de los aprendidos en clase?</t>
+  </si>
 </sst>
 </file>
 
@@ -344,13 +325,6 @@
     <font>
       <sz val="8"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
@@ -360,6 +334,13 @@
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -386,13 +367,15 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -734,8 +717,8 @@
   <cols>
     <col min="2" max="2" width="31.7109375" customWidth="1"/>
     <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="93.140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="68.7109375" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="105.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="94.140625" customWidth="1"/>
     <col min="8" max="8" width="42.28515625" customWidth="1"/>
@@ -751,7 +734,7 @@
       <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -777,7 +760,7 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
@@ -800,7 +783,7 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
@@ -810,13 +793,13 @@
         <v>2</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -836,7 +819,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -856,7 +839,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -876,7 +859,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="63" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -886,9 +869,10 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>24</v>
       </c>
+      <c r="E7" s="3"/>
       <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
@@ -896,7 +880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -906,8 +890,8 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>32</v>
+      <c r="D8" s="5" t="s">
+        <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>26</v>
@@ -916,7 +900,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -936,7 +920,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -946,8 +930,8 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>30</v>
+      <c r="D10" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>29</v>
@@ -966,14 +950,17 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="H11">
         <v>5</v>
@@ -989,17 +976,17 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>36</v>
+      <c r="D12" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1015,17 +1002,17 @@
       <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>42</v>
+      <c r="D13" s="3" t="s">
+        <v>40</v>
       </c>
       <c r="E13" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1041,17 +1028,17 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>46</v>
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>44</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1067,17 +1054,17 @@
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>49</v>
+      <c r="D15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>47</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -1093,17 +1080,17 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>51</v>
+      <c r="D16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>49</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -1119,17 +1106,17 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>53</v>
+      <c r="D17" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -1145,17 +1132,17 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>57</v>
+      <c r="D18" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1171,17 +1158,17 @@
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>57</v>
+      <c r="D19" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1197,17 +1184,17 @@
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>57</v>
+      <c r="D20" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -1223,7 +1210,7 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="3"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -1232,7 +1219,7 @@
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1241,13 +1228,13 @@
       <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" s="3"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="D24" s="2"/>
+      <c r="D24" s="3"/>
     </row>
     <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1259,17 +1246,17 @@
       <c r="C25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>39</v>
+      <c r="D25" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="E25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -1285,17 +1272,17 @@
       <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>57</v>
+      <c r="D26" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -1311,17 +1298,17 @@
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
+      <c r="D27" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -1337,17 +1324,17 @@
       <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>57</v>
+      <c r="D28" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="E28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H28">
         <v>5</v>
@@ -1363,7 +1350,7 @@
       <c r="C29" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="2"/>
+      <c r="D29" s="3"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30">
@@ -1375,28 +1362,28 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="2"/>
+      <c r="D30" s="3"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D31" s="2"/>
+      <c r="D31" s="3"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D32" s="2"/>
+      <c r="D32" s="3"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="2"/>
+      <c r="D33" s="3"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="2"/>
+      <c r="D34" s="3"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="2"/>
+      <c r="D35" s="3"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="2"/>
+      <c r="D36" s="3"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="2"/>
+      <c r="D37" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C86034B-7A91-4DD3-9BA1-76C3422984A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C74226-8F88-46CB-9EC7-836EF281F185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28095" yWindow="1440" windowWidth="26100" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-28740" yWindow="-900" windowWidth="27090" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="71">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +138,106 @@
   </si>
   <si>
     <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/nudosportada.jpg</t>
+  </si>
+  <si>
+    <t>Estáticas|Dinámicas|Semiestáticas|Cualquier tipo de cuerda</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/tiposdecuerdas.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Después de haber escogido la vía, el escalador comprueba que la longitud de
+la cuerda es la adecuada. También comprueba que no hay una gran diferencia
+de peso con su asegurador. Antes de empezar, asegurador y escalador
+realizan una comprobación mutua del equipo. Esta acción se denomina en escalada: </t>
+  </si>
+  <si>
+    <t>Rapelar|Chapar|Partner Check|Asegurar</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partnercheck.jpg</t>
+  </si>
+  <si>
+    <t>En la imagen ves una acción que permite limitar las consecuencias de una caída del escalador en los
+primeros metros de escalada, antes de que haya mosquetoneado el primer
+punto de seguridad. No sirve para retener al escalador, pero permite
+evitar las consecuencias de una mala caída. Sabrías decir como se llama esa acción en escalada:</t>
+  </si>
+  <si>
+    <t>Rapelar|Asegurar|Partner Check|Portear</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/portear.jpg</t>
+  </si>
+  <si>
+    <t>En la imagen vemos la gestualidad universal par utilizar correctamente un aparato para asegurar (gri-gri, reverso…) esa posición de las manos es fundamental. ¿Qué accion nunca debemos hacer cuando estamos realizando esa maniobra de aseguramiento?</t>
+  </si>
+  <si>
+    <t>Soltar la mano de frenado|Fijarte en el compañero para dar cuerda o recoger|Mantener una posición estable en el suelo|Bajar el centro de gravedad y ampliar base de sustentación</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/manodefrenado.jpg</t>
+  </si>
+  <si>
+    <t>El rol del asegurador no se limita a dar cuerda rápidamente y en el momento oportuno. Al permanecer concentrado en el escalador, el asegurador puede ver los momentos de tensión que requieren la máxima precisión y capacidad de reacción. ¿Cuál va a ser la labor más importante durante la ascensión del compañero?</t>
+  </si>
+  <si>
+    <t>Vigilancia|Anticipación|Movilidad|Vigilancia, anticipación y movilidad</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/vigilanci.jpg</t>
+  </si>
+  <si>
+    <t>Saltar y levantar la mano de la cuerda|Agarrar la cuerda que va al escalador y la que sale del sistema de retención|No hay que hacer nada porque se bloquea con el descensor|Sujetar firmemente la cuerda lado frenado, y al mismo tiempo tirar de ella hacia abajo</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/caidaescalada.jpg</t>
+  </si>
+  <si>
+    <t>Agarradas a la cuerda que sujeta al arnés|Agarrando las presas por las que va pasando durante el descenso|Deben estar sin sujetar la cuerda y preparadas por si tienen colocarse en el muro en caso de deplome|Agarrando el nudo de ocho doble</t>
+  </si>
+  <si>
+    <t>Cuando el escalador está listo para descender, después de la señal acordada, se deja llevar por la cuerda y no tiene ninguna forma de controlar el descenso. Toda la responsabilidad de esta maniobra recae en el asegurador, que tiene la vida del escalador en sus manos .¿Cómo debe colocar las manos durante el descenso el escalador?</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/descenso.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/arnes.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En la siguiente imagen vemos un material que usamos en escalada que se denomina: </t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Grigri</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/mosquetonseguridad.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/grigri.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lineadevida.jpg</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/cintaesprexx.jpg</t>
+  </si>
+  <si>
+    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Pies de gato</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/piedegato.jpg</t>
+  </si>
+  <si>
+    <t>En caso de caída, independientemente del aparato utilizado, la acción
+que debemos hacer para aumentar el rozamiento y frenar la caida es:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Nudo Vuelta de Braza o Nudo Leñador sirve principalmente para asegurar una cuerda de forma rápida y segura a troncos, postes, maderas o ramas para arrastrarlos, elevarlos o fijarlos.  Haz el nudo y sube la imagen. </t>
+  </si>
+  <si>
+    <t>Tienes que unir dos cuerdas de grosores muy distintos. ¿Qué nudo utilizarías de los aprendidos en clase?</t>
   </si>
   <si>
     <r>
@@ -146,7 +246,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -155,7 +255,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -165,7 +265,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -174,7 +274,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -184,7 +284,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -193,7 +293,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos"/>
         <family val="2"/>
@@ -202,104 +302,19 @@
     </r>
   </si>
   <si>
-    <t>Estáticas|Dinámicas|Semiestáticas|Cualquier tipo de cuerda</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/tiposdecuerdas.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Después de haber escogido la vía, el escalador comprueba que la longitud de
-la cuerda es la adecuada. También comprueba que no hay una gran diferencia
-de peso con su asegurador. Antes de empezar, asegurador y escalador
-realizan una comprobación mutua del equipo. Esta acción se denomina en escalada: </t>
-  </si>
-  <si>
-    <t>Rapelar|Chapar|Partner Check|Asegurar</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/partnercheck.jpg</t>
-  </si>
-  <si>
-    <t>En la imagen ves una acción que permite limitar las consecuencias de una caída del escalador en los
-primeros metros de escalada, antes de que haya mosquetoneado el primer
-punto de seguridad. No sirve para retener al escalador, pero permite
-evitar las consecuencias de una mala caída. Sabrías decir como se llama esa acción en escalada:</t>
-  </si>
-  <si>
-    <t>Rapelar|Asegurar|Partner Check|Portear</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/portear.jpg</t>
-  </si>
-  <si>
-    <t>En la imagen vemos la gestualidad universal par utilizar correctamente un aparato para asegurar (gri-gri, reverso…) esa posición de las manos es fundamental. ¿Qué accion nunca debemos hacer cuando estamos realizando esa maniobra de aseguramiento?</t>
-  </si>
-  <si>
-    <t>Soltar la mano de frenado|Fijarte en el compañero para dar cuerda o recoger|Mantener una posición estable en el suelo|Bajar el centro de gravedad y ampliar base de sustentación</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/manodefrenado.jpg</t>
-  </si>
-  <si>
-    <t>El rol del asegurador no se limita a dar cuerda rápidamente y en el momento oportuno. Al permanecer concentrado en el escalador, el asegurador puede ver los momentos de tensión que requieren la máxima precisión y capacidad de reacción. ¿Cuál va a ser la labor más importante durante la ascensión del compañero?</t>
-  </si>
-  <si>
-    <t>Vigilancia|Anticipación|Movilidad|Vigilancia, anticipación y movilidad</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/vigilanci.jpg</t>
-  </si>
-  <si>
-    <t>Saltar y levantar la mano de la cuerda|Agarrar la cuerda que va al escalador y la que sale del sistema de retención|No hay que hacer nada porque se bloquea con el descensor|Sujetar firmemente la cuerda lado frenado, y al mismo tiempo tirar de ella hacia abajo</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/caidaescalada.jpg</t>
-  </si>
-  <si>
-    <t>Agarradas a la cuerda que sujeta al arnés|Agarrando las presas por las que va pasando durante el descenso|Deben estar sin sujetar la cuerda y preparadas por si tienen colocarse en el muro en caso de deplome|Agarrando el nudo de ocho doble</t>
-  </si>
-  <si>
-    <t>Cuando el escalador está listo para descender, después de la señal acordada, se deja llevar por la cuerda y no tiene ninguna forma de controlar el descenso. Toda la responsabilidad de esta maniobra recae en el asegurador, que tiene la vida del escalador en sus manos .¿Cómo debe colocar las manos durante el descenso el escalador?</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/descenso.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/arnes.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">En la siguiente imagen vemos un material que usamos en escalada que se denomina: </t>
-  </si>
-  <si>
-    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Grigri</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/mosquetonseguridad.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/grigri.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lineadevida.jpg</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/cintaesprexx.jpg</t>
-  </si>
-  <si>
-    <t>Arnés|Mosquetón de seguridad|Cinta Express|Linea de Vida|Pies de gato</t>
-  </si>
-  <si>
-    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/piedegato.jpg</t>
-  </si>
-  <si>
-    <t>En caso de caída, independientemente del aparato utilizado, la acción
-que debemos hacer para aumentar el rozamiento y frenar la caida es:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Nudo Vuelta de Braza o Nudo Leñador sirve principalmente para asegurar una cuerda de forma rápida y segura a troncos, postes, maderas o ramas para arrastrarlos, elevarlos o fijarlos.  Haz el nudo y sube la imagen. </t>
-  </si>
-  <si>
-    <t>Tienes que unir dos cuerdas de grosores muy distintos. ¿Qué nudo utilizarías de los aprendidos en clase?</t>
+    <t>La escalada hace su debut Olímpico en los Juegos de Tokyo 2020 (aplazados al 2021). Los escaladores ponen a examen sus habilidades -físicas y mentalesen una pared vertical con ángulos variables y con secciones positivas y negativas (estructuras y desplomes, respectivamente). Una de las modalidasde que implementan consiste en:  dos escaladores se enfrentan el uno al otro, asegurados con cuerdas de seguridad, deben ascender por una pared de 15 metros de altura y una inclinación de 95 grados, recorriendo vías idénticas, y deben hacerlo más rápido que su oponente. ¿De que modalidad se trata?</t>
+  </si>
+  <si>
+    <t>Boulder o escalada en bloque|Velocidad|Lead o dificultad|</t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/bloque.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Una prueba olimpica donde los escaladores intentan escalar lo más alto posible en una pared de más de 15m de altura, y tienen 6 minutos para hacerlo. Si uno se cae, se registra la altura máxima alcanzada y no vuelve a subir. Nos estamos refiriendo a la prueba de: </t>
+  </si>
+  <si>
+    <t>https://github.com/josecarlostejedor/evaluacion-escalada/blob/main/lead.jpg</t>
   </si>
 </sst>
 </file>
@@ -323,24 +338,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="8"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -367,15 +382,15 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -715,10 +730,10 @@
   <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="31.7109375" customWidth="1"/>
-    <col min="3" max="3" width="72.85546875" customWidth="1"/>
-    <col min="4" max="4" width="93.140625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="105.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="65.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="94.140625" customWidth="1"/>
     <col min="8" max="8" width="42.28515625" customWidth="1"/>
@@ -734,7 +749,7 @@
       <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -760,7 +775,7 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
@@ -783,7 +798,7 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
@@ -809,7 +824,7 @@
       <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
@@ -829,7 +844,7 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
@@ -849,7 +864,7 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>23</v>
       </c>
       <c r="G6" s="1" t="s">
@@ -869,10 +884,10 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="3"/>
+      <c r="E7" s="2"/>
       <c r="G7" s="1" t="s">
         <v>25</v>
       </c>
@@ -890,7 +905,7 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -910,7 +925,7 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -930,8 +945,8 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>64</v>
+      <c r="D10" s="4" t="s">
+        <v>63</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>29</v>
@@ -950,8 +965,8 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>65</v>
+      <c r="D11" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>32</v>
@@ -976,17 +991,17 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" t="s">
         <v>34</v>
-      </c>
-      <c r="E12" t="s">
-        <v>35</v>
       </c>
       <c r="F12">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12">
         <v>5</v>
@@ -1002,17 +1017,17 @@
       <c r="C13" t="s">
         <v>10</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" t="s">
         <v>40</v>
-      </c>
-      <c r="E13" t="s">
-        <v>41</v>
       </c>
       <c r="F13">
         <v>3</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13">
         <v>5</v>
@@ -1028,17 +1043,17 @@
       <c r="C14" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F14">
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H14">
         <v>5</v>
@@ -1054,17 +1069,17 @@
       <c r="C15" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="F15">
         <v>3</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H15">
         <v>5</v>
@@ -1080,17 +1095,17 @@
       <c r="C16" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>49</v>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H16">
         <v>5</v>
@@ -1106,17 +1121,17 @@
       <c r="C17" t="s">
         <v>10</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>51</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="F17">
         <v>2</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H17">
         <v>5</v>
@@ -1132,17 +1147,17 @@
       <c r="C18" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" t="s">
         <v>55</v>
-      </c>
-      <c r="E18" t="s">
-        <v>56</v>
       </c>
       <c r="F18">
         <v>0</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H18">
         <v>5</v>
@@ -1158,17 +1173,17 @@
       <c r="C19" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" t="s">
         <v>55</v>
-      </c>
-      <c r="E19" t="s">
-        <v>56</v>
       </c>
       <c r="F19">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H19">
         <v>5</v>
@@ -1184,17 +1199,17 @@
       <c r="C20" t="s">
         <v>10</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="s">
         <v>55</v>
-      </c>
-      <c r="E20" t="s">
-        <v>56</v>
       </c>
       <c r="F20">
         <v>4</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H20">
         <v>5</v>
@@ -1210,7 +1225,7 @@
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="3"/>
+      <c r="D21" s="2"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22">
@@ -1219,7 +1234,7 @@
       <c r="C22" t="s">
         <v>12</v>
       </c>
-      <c r="D22" s="3"/>
+      <c r="D22" s="2"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23">
@@ -1228,13 +1243,13 @@
       <c r="C23" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="3"/>
+      <c r="D23" s="2"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>23</v>
       </c>
-      <c r="D24" s="3"/>
+      <c r="D24" s="2"/>
     </row>
     <row r="25" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A25">
@@ -1246,17 +1261,17 @@
       <c r="C25" t="s">
         <v>10</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" t="s">
         <v>37</v>
-      </c>
-      <c r="E25" t="s">
-        <v>38</v>
       </c>
       <c r="F25">
         <v>2</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H25">
         <v>5</v>
@@ -1272,17 +1287,17 @@
       <c r="C26" t="s">
         <v>10</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="D26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E26" t="s">
         <v>55</v>
-      </c>
-      <c r="E26" t="s">
-        <v>56</v>
       </c>
       <c r="F26">
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H26">
         <v>5</v>
@@ -1298,17 +1313,17 @@
       <c r="C27" t="s">
         <v>10</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="D27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" t="s">
         <v>55</v>
-      </c>
-      <c r="E27" t="s">
-        <v>56</v>
       </c>
       <c r="F27">
         <v>2</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H27">
         <v>5</v>
@@ -1324,23 +1339,23 @@
       <c r="C28" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>55</v>
+      <c r="D28" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="E28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F28">
         <v>4</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="90" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1350,9 +1365,23 @@
       <c r="C29" t="s">
         <v>10</v>
       </c>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E29" t="s">
+        <v>67</v>
+      </c>
+      <c r="F29">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1362,28 +1391,42 @@
       <c r="C30" t="s">
         <v>10</v>
       </c>
-      <c r="D30" s="3"/>
+      <c r="D30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E30" t="s">
+        <v>67</v>
+      </c>
+      <c r="F30">
+        <v>2</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30">
+        <v>5</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D31" s="3"/>
+      <c r="D31" s="2"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D32" s="3"/>
+      <c r="D32" s="2"/>
     </row>
     <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="3"/>
+      <c r="D33" s="2"/>
     </row>
     <row r="34" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D34" s="3"/>
+      <c r="D34" s="2"/>
     </row>
     <row r="35" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D35" s="3"/>
+      <c r="D35" s="2"/>
     </row>
     <row r="36" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D36" s="3"/>
+      <c r="D36" s="2"/>
     </row>
     <row r="37" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D37" s="3"/>
+      <c r="D37" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1409,6 +1452,8 @@
     <hyperlink ref="G26" r:id="rId20" xr:uid="{9F92CBA7-5E57-412F-BEA4-6893071DBB45}"/>
     <hyperlink ref="G27" r:id="rId21" xr:uid="{8E1A4167-6259-4D9F-AE04-9B5E6C4ED88B}"/>
     <hyperlink ref="G28" r:id="rId22" xr:uid="{2E8A41EB-EB16-48D9-AF87-44431ED6BA50}"/>
+    <hyperlink ref="G29" r:id="rId23" xr:uid="{BDC7B29F-8EE6-4FBB-B55C-21A91FD0DDFE}"/>
+    <hyperlink ref="G30" r:id="rId24" xr:uid="{87581434-84E5-469B-AC81-C4986736CBC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/preguntasescalada.xlsx
+++ b/preguntasescalada.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jose Carlos\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{15C74226-8F88-46CB-9EC7-836EF281F185}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5AA93962-D30C-48AA-B7A8-1AF1ACFDDE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28740" yWindow="-900" windowWidth="27090" windowHeight="10695" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
+    <workbookView xWindow="-28920" yWindow="-1110" windowWidth="29040" windowHeight="15720" xr2:uid="{27582EAC-85B6-488A-A3CF-EAED546E386D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -379,13 +379,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -732,7 +731,7 @@
   <cols>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
     <col min="3" max="3" width="25.5703125" customWidth="1"/>
-    <col min="4" max="4" width="93.140625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="93.140625" customWidth="1"/>
     <col min="5" max="5" width="65.85546875" customWidth="1"/>
     <col min="6" max="6" width="16.85546875" customWidth="1"/>
     <col min="7" max="7" width="94.140625" customWidth="1"/>
@@ -749,7 +748,7 @@
       <c r="C1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
@@ -775,7 +774,7 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" t="s">
         <v>14</v>
       </c>
       <c r="E2" t="s">
@@ -798,7 +797,7 @@
       <c r="C3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
       <c r="E3" t="s">
@@ -884,7 +883,7 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E7" s="2"/>
@@ -905,7 +904,7 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="1" t="s">
@@ -945,7 +944,7 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G10" s="1" t="s">
@@ -965,7 +964,7 @@
       <c r="C11" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" t="s">
         <v>64</v>
       </c>
       <c r="E11" t="s">
@@ -991,7 +990,7 @@
       <c r="C12" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>65</v>
       </c>
       <c r="E12" t="s">
@@ -1372,7 +1371,7 @@
         <v>67</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>68</v>
